--- a/data/sampleWorkbook.xlsx
+++ b/data/sampleWorkbook.xlsx
@@ -706,7 +706,7 @@
         <v>560102</v>
       </c>
       <c r="F8">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G8">
         <v>6</v>
@@ -882,7 +882,7 @@
         <v>560043</v>
       </c>
       <c r="F12">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -979,7 +979,7 @@
         <v>Runs a bakery</v>
       </c>
       <c r="I14" t="str">
-        <v>Owned</v>
+        <v>Rented</v>
       </c>
       <c r="J14">
         <v>500</v>
@@ -1052,7 +1052,7 @@
         <v>560029</v>
       </c>
       <c r="F16">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1096,7 +1096,7 @@
         <v>560029</v>
       </c>
       <c r="F17">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="G17">
         <v>2</v>
@@ -1272,7 +1272,7 @@
         <v>572102</v>
       </c>
       <c r="F21">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -1316,7 +1316,7 @@
         <v>560037</v>
       </c>
       <c r="F22">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -1530,7 +1530,7 @@
         <v>560036</v>
       </c>
       <c r="F27">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="G27">
         <v>3</v>
@@ -1571,7 +1571,7 @@
         <v>Karnataka</v>
       </c>
       <c r="E28">
-        <v>570020</v>
+        <v>570023</v>
       </c>
       <c r="F28">
         <v>38</v>
@@ -1615,7 +1615,7 @@
         <v>Karnataka</v>
       </c>
       <c r="E29">
-        <v>570008</v>
+        <v>570020</v>
       </c>
       <c r="F29">
         <v>45</v>
@@ -1630,7 +1630,7 @@
         <v>Not yet identified</v>
       </c>
       <c r="L29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M29" t="str">
         <v>Kannada</v>
@@ -1982,6 +1982,182 @@
         <v>Kannada</v>
       </c>
       <c r="N37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>APP-034</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Prakash Hegde</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Mysuru</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Karnataka</v>
+      </c>
+      <c r="E38">
+        <v>570009</v>
+      </c>
+      <c r="F38">
+        <v>40</v>
+      </c>
+      <c r="G38">
+        <v>6</v>
+      </c>
+      <c r="H38" t="str">
+        <v>Footwear retail</v>
+      </c>
+      <c r="I38" t="str">
+        <v>Owned</v>
+      </c>
+      <c r="J38">
+        <v>600</v>
+      </c>
+      <c r="K38" t="str">
+        <v>Ground</v>
+      </c>
+      <c r="L38">
+        <v>4</v>
+      </c>
+      <c r="M38" t="str">
+        <v>Kannada</v>
+      </c>
+      <c r="N38" t="str">
+        <v>Own a shop in Saraswathipuram</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>APP-035</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Lokesh Reddy</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Bengaluru</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Karnataka</v>
+      </c>
+      <c r="E39">
+        <v>560037</v>
+      </c>
+      <c r="F39">
+        <v>60</v>
+      </c>
+      <c r="G39">
+        <v>6</v>
+      </c>
+      <c r="H39" t="str">
+        <v>Electronics retail</v>
+      </c>
+      <c r="I39" t="str">
+        <v>Rented</v>
+      </c>
+      <c r="J39">
+        <v>600</v>
+      </c>
+      <c r="K39" t="str">
+        <v>Ground</v>
+      </c>
+      <c r="L39">
+        <v>4</v>
+      </c>
+      <c r="M39" t="str">
+        <v>English</v>
+      </c>
+      <c r="N39" t="str">
+        <v>Shop on the ground floor with the first floor used for storage</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>APP-036</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Ravi Kumar</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Davanagere</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Karnataka</v>
+      </c>
+      <c r="E40">
+        <v>577002</v>
+      </c>
+      <c r="F40">
+        <v>30</v>
+      </c>
+      <c r="G40">
+        <v>4</v>
+      </c>
+      <c r="H40" t="str">
+        <v>Footwear retail</v>
+      </c>
+      <c r="I40" t="str">
+        <v>Rented</v>
+      </c>
+      <c r="J40">
+        <v>450</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Ground</v>
+      </c>
+      <c r="L40">
+        <v>4</v>
+      </c>
+      <c r="M40" t="str">
+        <v>Kannada</v>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>APP-037</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Ravi K</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Mangaluru</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Karnataka</v>
+      </c>
+      <c r="E41">
+        <v>575003</v>
+      </c>
+      <c r="F41">
+        <v>28</v>
+      </c>
+      <c r="G41">
+        <v>2</v>
+      </c>
+      <c r="H41" t="str">
+        <v>Mobile accessories</v>
+      </c>
+      <c r="I41" t="str">
+        <v>Rented</v>
+      </c>
+      <c r="J41">
+        <v>400</v>
+      </c>
+      <c r="K41" t="str">
+        <v>Ground</v>
+      </c>
+      <c r="L41">
+        <v>4</v>
+      </c>
+      <c r="M41" t="str">
+        <v>English</v>
+      </c>
+      <c r="N41" t="str">
         <v/>
       </c>
     </row>
@@ -2098,7 +2274,7 @@
         <v>Karnataka</v>
       </c>
       <c r="D5" t="str">
-        <v>560038, 560037, 560048, 560036, 560093, 560047</v>
+        <v>560038, 560037, 560048, 560036, 560093, 560047, 560017</v>
       </c>
       <c r="E5" t="str">
         <v>Tier 1</v>
@@ -2144,13 +2320,13 @@
         <v>Karnataka</v>
       </c>
       <c r="D7" t="str">
-        <v>570005, 570008, 570009, 570010, 570015, 570020</v>
+        <v>570004, 570005, 570009, 570010, 570015, 570020</v>
       </c>
       <c r="E7" t="str">
         <v>Tier 1</v>
       </c>
       <c r="F7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7" t="str">
         <v>High</v>

--- a/data/sampleWorkbook.xlsx
+++ b/data/sampleWorkbook.xlsx
@@ -1269,7 +1269,7 @@
         <v>Karnataka</v>
       </c>
       <c r="E21">
-        <v>572102</v>
+        <v>572106</v>
       </c>
       <c r="F21">
         <v>12</v>
@@ -2320,7 +2320,7 @@
         <v>Karnataka</v>
       </c>
       <c r="D7" t="str">
-        <v>570004, 570005, 570009, 570010, 570015, 570020</v>
+        <v>570004, 570005, 570009, 570010, 570015, 570016, 570020</v>
       </c>
       <c r="E7" t="str">
         <v>Tier 1</v>
@@ -2366,7 +2366,7 @@
         <v>Karnataka</v>
       </c>
       <c r="D9" t="str">
-        <v>572101, 572102, 577001</v>
+        <v>572101, 572106, 577001</v>
       </c>
       <c r="E9" t="str">
         <v>Tier 3</v>

--- a/data/sampleWorkbook.xlsx
+++ b/data/sampleWorkbook.xlsx
@@ -2297,13 +2297,13 @@
         <v>Karnataka</v>
       </c>
       <c r="D6" t="str">
-        <v>560024; 560032; 560043; 560084; 560045; 560077</v>
+        <v>560024; 560032; 560043; 560084; 560045; 560077; 560058</v>
       </c>
       <c r="E6" t="str">
         <v>Tier 1</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6" t="str">
         <v>Low</v>

--- a/data/sampleWorkbook.xlsx
+++ b/data/sampleWorkbook.xlsx
@@ -1888,7 +1888,7 @@
         <v>Ground</v>
       </c>
       <c r="L35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M35" t="str">
         <v>Kannada</v>
